--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="169">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -629,10 +629,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"scope":"self", "stat":"hp","m":0.1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"endurance":360</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -727,6 +723,18 @@
   </si>
   <si>
     <t>{"cond":"attack","scope":"enemy","type":"dot","value":2,"dur":3,"icon":"icons:0","tag":"bleed"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"scope":"self", "stat":"hunger","m":0.1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"scope":"self", "stat":"hunger","m":0.2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"scope":"self", "stat":"thirst","m":-0.5}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1166,7 +1174,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D3" s="3">
         <v>10</v>
@@ -1189,7 +1197,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D4" s="3">
         <v>10</v>
@@ -1215,7 +1223,7 @@
         <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D5" s="3">
         <v>10</v>
@@ -1246,10 +1254,13 @@
         <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D7" s="3">
         <v>10</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>166</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>41</v>
@@ -1272,10 +1283,13 @@
         <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D8" s="3">
         <v>15</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>167</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>42</v>
@@ -1298,10 +1312,13 @@
         <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D9" s="3">
         <v>10</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>166</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>42</v>
@@ -1324,10 +1341,13 @@
         <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" s="3">
         <v>15</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>167</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>43</v>
@@ -1356,13 +1376,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D12" s="3">
         <v>15</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>140</v>
@@ -1371,7 +1391,7 @@
         <v>141</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>116</v>
@@ -1391,7 +1411,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D13" s="3">
         <v>25</v>
@@ -1417,7 +1437,7 @@
         <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D14" s="3">
         <v>35</v>
@@ -1440,13 +1460,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D15" s="3">
         <v>35</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>114</v>
@@ -1466,13 +1486,13 @@
         <v>9</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D16" s="3">
         <v>35</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>115</v>
@@ -1553,7 +1573,7 @@
         <v>10</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D20" s="3">
         <v>30</v>
@@ -1637,7 +1657,7 @@
         <v>11</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D24" s="3">
         <v>60</v>
@@ -1782,7 +1802,7 @@
         <v>14</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D31" s="3">
         <v>10</v>
@@ -1802,7 +1822,7 @@
         <v>15</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D32" s="3">
         <v>10</v>
@@ -1822,13 +1842,13 @@
         <v>16</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D34" s="3">
         <v>10</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>117</v>
@@ -1845,16 +1865,16 @@
         <v>19</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D35" s="3">
         <v>10</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>118</v>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -625,10 +625,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"cond":"attack","scope":"self", "stat":"atk","m":0.05}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"endurance":360</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -735,6 +731,16 @@
   </si>
   <si>
     <t>{"scope":"self", "stat":"thirst","m":-0.5}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"stage":"atk", "scope":"self",   "type":"mod",    "key":"acc",   "m":0.1},
+{"stage":"atk", "scope":"target", "type":"mod",    "key":"eva",   "m":-0.1},
+{"stage":"hit", "scope":"target", "type":"dot",    "a":-1,        "dur":3,    "id":"poison", "tcon":"🩸"},
+{"stage":"hit", "scope":"target", "type":"dot",    "m":-0.1,        "dur":3,    "id":"fire", "tcon":"🔥" },
+{"stage":"hit", "scope":"target", "type":"debuff", "chance":0.5,  "dur":1,    "id":"stun", "tcon":"💫"},
+{"stage":"hit", "scope":"self",   "type":"action", "chance":0.25, "key":"hp", "m":0.25, "id":"lifesteal"},
+{"stage":"hit", "scope":"self",   "type":"buff", "chance":0.25, "key":"str", "a":1, "dur":3, "id":"strong", "tcon":"💪"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1117,7 +1123,7 @@
     <col min="5" max="5" width="48.33203125" style="3" customWidth="1"/>
     <col min="6" max="6" width="35.33203125" style="3" customWidth="1"/>
     <col min="7" max="7" width="33.88671875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="60.77734375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="102.33203125" style="3" customWidth="1"/>
     <col min="9" max="9" width="72.109375" style="3" customWidth="1"/>
     <col min="10" max="10" width="37.44140625" style="3" customWidth="1"/>
     <col min="11" max="16384" width="21.33203125" style="3"/>
@@ -1174,7 +1180,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D3" s="3">
         <v>10</v>
@@ -1197,7 +1203,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D4" s="3">
         <v>10</v>
@@ -1223,7 +1229,7 @@
         <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D5" s="3">
         <v>10</v>
@@ -1254,13 +1260,13 @@
         <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D7" s="3">
         <v>10</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>41</v>
@@ -1283,13 +1289,13 @@
         <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D8" s="3">
         <v>15</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>42</v>
@@ -1312,13 +1318,13 @@
         <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D9" s="3">
         <v>10</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>42</v>
@@ -1341,13 +1347,13 @@
         <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D10" s="3">
         <v>15</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>43</v>
@@ -1368,7 +1374,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="28.8">
+    <row r="12" spans="1:14" ht="100.8">
       <c r="A12" s="4" t="s">
         <v>24</v>
       </c>
@@ -1376,22 +1382,22 @@
         <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D12" s="3">
         <v>15</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>140</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>116</v>
@@ -1411,7 +1417,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D13" s="3">
         <v>25</v>
@@ -1437,7 +1443,7 @@
         <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D14" s="3">
         <v>35</v>
@@ -1460,13 +1466,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D15" s="3">
         <v>35</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>114</v>
@@ -1486,13 +1492,13 @@
         <v>9</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D16" s="3">
         <v>35</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>115</v>
@@ -1573,7 +1579,7 @@
         <v>10</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D20" s="3">
         <v>30</v>
@@ -1657,7 +1663,7 @@
         <v>11</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D24" s="3">
         <v>60</v>
@@ -1802,7 +1808,7 @@
         <v>14</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D31" s="3">
         <v>10</v>
@@ -1822,7 +1828,7 @@
         <v>15</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D32" s="3">
         <v>10</v>
@@ -1842,13 +1848,13 @@
         <v>16</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D34" s="3">
         <v>10</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>117</v>
@@ -1865,16 +1871,16 @@
         <v>19</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D35" s="3">
         <v>10</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>118</v>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -722,25 +722,26 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"scope":"self", "stat":"hunger","m":0.1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"scope":"self", "stat":"hunger","m":0.2}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"scope":"self", "stat":"thirst","m":-0.5}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"stage":"atk", "scope":"self",   "type":"mod",    "key":"acc",   "m":0.1},
+    <t>{"type":"mod", "key":"str",   "a":1},
+{"stage":"atk", "scope":"self",   "type":"mod",    "key":"acc",   "m":0.1},
 {"stage":"atk", "scope":"target", "type":"mod",    "key":"eva",   "m":-0.1},
 {"stage":"hit", "scope":"target", "type":"dot",    "a":-1,        "dur":3,    "id":"poison", "tcon":"🩸"},
 {"stage":"hit", "scope":"target", "type":"dot",    "m":-0.1,        "dur":3,    "id":"fire", "tcon":"🔥" },
 {"stage":"hit", "scope":"target", "type":"debuff", "chance":0.5,  "dur":1,    "id":"stun", "tcon":"💫"},
 {"stage":"hit", "scope":"self",   "type":"action", "chance":0.25, "key":"hp", "m":0.25, "id":"lifesteal"},
 {"stage":"hit", "scope":"self",   "type":"buff", "chance":0.25, "key":"str", "a":1, "dur":3, "id":"strong", "tcon":"💪"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"scope":"self", "key":"hunger","m":0.1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"scope":"self", "key":"hunger","m":0.2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"scope":"self", "key":"thirst","m":-0.5}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1266,7 +1267,7 @@
         <v>10</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>41</v>
@@ -1295,7 +1296,7 @@
         <v>15</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>42</v>
@@ -1324,7 +1325,7 @@
         <v>10</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>42</v>
@@ -1353,7 +1354,7 @@
         <v>15</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>43</v>
@@ -1374,7 +1375,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="100.8">
+    <row r="12" spans="1:14" ht="115.2">
       <c r="A12" s="4" t="s">
         <v>24</v>
       </c>
@@ -1394,7 +1395,7 @@
         <v>140</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>164</v>
@@ -1877,7 +1878,7 @@
         <v>10</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>142</v>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -722,26 +722,26 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>{"scope":"self", "key":"hunger","m":0.1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"scope":"self", "key":"hunger","m":0.2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"scope":"self", "key":"thirst","m":-0.5}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>{"type":"mod", "key":"str",   "a":1},
 {"stage":"atk", "scope":"self",   "type":"mod",    "key":"acc",   "m":0.1},
 {"stage":"atk", "scope":"target", "type":"mod",    "key":"eva",   "m":-0.1},
-{"stage":"hit", "scope":"target", "type":"dot",    "a":-1,        "dur":3,    "id":"poison", "tcon":"🩸"},
-{"stage":"hit", "scope":"target", "type":"dot",    "m":-0.1,        "dur":3,    "id":"fire", "tcon":"🔥" },
-{"stage":"hit", "scope":"target", "type":"debuff", "chance":0.5,  "dur":1,    "id":"stun", "tcon":"💫"},
+{"stage":"hit", "scope":"target", "type":"dot",    "a":-1,        "dur":3,    "id":"poison", "icon":"🩸"},
+{"stage":"hit", "scope":"target", "type":"dot",    "m":-0.1,        "dur":3,    "id":"fire", "icon":"🔥" },
+{"stage":"hit", "scope":"target", "type":"debuff", "chance":0.5,  "dur":1,    "id":"stun", "icon":"💫"},
 {"stage":"hit", "scope":"self",   "type":"action", "chance":0.25, "key":"hp", "m":0.25, "id":"lifesteal"},
-{"stage":"hit", "scope":"self",   "type":"buff", "chance":0.25, "key":"str", "a":1, "dur":3, "id":"strong", "tcon":"💪"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"scope":"self", "key":"hunger","m":0.1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"scope":"self", "key":"hunger","m":0.2}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"scope":"self", "key":"thirst","m":-0.5}</t>
+{"stage":"hit", "scope":"self",   "type":"buff", "chance":0.25, "key":"str", "a":1, "dur":3, "id":"strong", "icon":"💪"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1267,7 +1267,7 @@
         <v>10</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>41</v>
@@ -1296,7 +1296,7 @@
         <v>15</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>42</v>
@@ -1325,7 +1325,7 @@
         <v>10</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>42</v>
@@ -1354,7 +1354,7 @@
         <v>15</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>43</v>
@@ -1395,7 +1395,7 @@
         <v>140</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>164</v>
@@ -1878,7 +1878,7 @@
         <v>10</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>142</v>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="171">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -496,10 +496,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"type":"melee","range":1,"atk":25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"type":"melee","range":1,"atk":35</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -569,11 +565,6 @@
   <si>
     <t>"lab":"熟肉",
 "des":"熟肉"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"lab":"鐵劍",
-"des":"鐵劍"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -742,6 +733,23 @@
 {"stage":"hit", "scope":"target", "type":"debuff", "chance":0.5,  "dur":1,    "id":"stun", "icon":"💫"},
 {"stage":"hit", "scope":"self",   "type":"action", "chance":0.25, "key":"hp", "m":0.25, "id":"lifesteal"},
 {"stage":"hit", "scope":"self",   "type":"buff", "chance":0.25, "key":"str", "a":1, "dur":3, "id":"strong", "icon":"💪"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"stage":"hit","scope":"target","type":"dot","a":-1,"dur":5,"stack":3,"elm":"poison","id":"posion", "icon":"☠️"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"type":"melee","range":1,"atk":5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"sprite":"weapons:3","y":22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"焠毒短劍",
+"des":"用毒液浸泡過的短劍，可使目標中毒"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1150,13 +1158,13 @@
         <v>45</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>20</v>
@@ -1181,7 +1189,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D3" s="3">
         <v>10</v>
@@ -1204,7 +1212,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D4" s="3">
         <v>10</v>
@@ -1230,7 +1238,7 @@
         <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D5" s="3">
         <v>10</v>
@@ -1261,19 +1269,19 @@
         <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D7" s="3">
         <v>10</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>41</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>74</v>
@@ -1290,19 +1298,19 @@
         <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D8" s="3">
         <v>15</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>75</v>
@@ -1319,19 +1327,19 @@
         <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D9" s="3">
         <v>10</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>42</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>76</v>
@@ -1348,19 +1356,19 @@
         <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D10" s="3">
         <v>15</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>43</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>77</v>
@@ -1383,25 +1391,25 @@
         <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D12" s="3">
         <v>15</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>78</v>
@@ -1410,7 +1418,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="28.8">
+    <row r="13" spans="1:14" ht="43.2">
       <c r="A13" s="4" t="s">
         <v>25</v>
       </c>
@@ -1418,16 +1426,22 @@
         <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D13" s="3">
         <v>25</v>
       </c>
+      <c r="E13" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="G13" s="3" t="s">
-        <v>112</v>
+        <v>168</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>167</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>79</v>
@@ -1444,13 +1458,16 @@
         <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D14" s="3">
         <v>35</v>
       </c>
+      <c r="E14" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="G14" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>93</v>
@@ -1467,22 +1484,22 @@
         <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D15" s="3">
         <v>35</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K15" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="L15" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="28.8">
@@ -1493,22 +1510,22 @@
         <v>9</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D16" s="3">
         <v>35</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1528,7 +1545,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>49</v>
@@ -1557,7 +1574,7 @@
         <v>20</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>60</v>
@@ -1580,7 +1597,7 @@
         <v>10</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D20" s="3">
         <v>30</v>
@@ -1612,7 +1629,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>46</v>
@@ -1641,7 +1658,7 @@
         <v>40</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>54</v>
@@ -1664,7 +1681,7 @@
         <v>11</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D24" s="3">
         <v>60</v>
@@ -1696,7 +1713,7 @@
         <v>10</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>52</v>
@@ -1725,7 +1742,7 @@
         <v>10</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>63</v>
@@ -1734,7 +1751,7 @@
         <v>111</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>87</v>
@@ -1754,7 +1771,7 @@
         <v>10</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>53</v>
@@ -1783,7 +1800,7 @@
         <v>10</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>58</v>
@@ -1792,7 +1809,7 @@
         <v>111</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>88</v>
@@ -1809,7 +1826,7 @@
         <v>14</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D31" s="3">
         <v>10</v>
@@ -1829,7 +1846,7 @@
         <v>15</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D32" s="3">
         <v>10</v>
@@ -1849,16 +1866,16 @@
         <v>16</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D34" s="3">
         <v>10</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>91</v>
@@ -1872,19 +1889,19 @@
         <v>19</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D35" s="3">
         <v>10</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>92</v>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -725,31 +725,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>{"stage":"hit","scope":"target","type":"dot","a":-1,"dur":5,"stack":3,"elm":"poison","id":"posion", "icon":"☠️"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"type":"melee","range":1,"atk":5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"sprite":"weapons:3","y":22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"焠毒短劍",
+"des":"用毒液浸泡過的短劍，可使目標中毒"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>{"type":"mod", "key":"str",   "a":1},
 {"stage":"atk", "scope":"self",   "type":"mod",    "key":"acc",   "m":0.1},
 {"stage":"atk", "scope":"target", "type":"mod",    "key":"eva",   "m":-0.1},
+{"stage":"hit", "scope":"target", "type":"debuff", "chance":0.5,  "dur":1,    "id":"stun", "icon":"💫"},
 {"stage":"hit", "scope":"target", "type":"dot",    "a":-1,        "dur":3,    "id":"poison", "icon":"🩸"},
 {"stage":"hit", "scope":"target", "type":"dot",    "m":-0.1,        "dur":3,    "id":"fire", "icon":"🔥" },
-{"stage":"hit", "scope":"target", "type":"debuff", "chance":0.5,  "dur":1,    "id":"stun", "icon":"💫"},
 {"stage":"hit", "scope":"self",   "type":"action", "chance":0.25, "key":"hp", "m":0.25, "id":"lifesteal"},
 {"stage":"hit", "scope":"self",   "type":"buff", "chance":0.25, "key":"str", "a":1, "dur":3, "id":"strong", "icon":"💪"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"stage":"hit","scope":"target","type":"dot","a":-1,"dur":5,"stack":3,"elm":"poison","id":"posion", "icon":"☠️"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"type":"melee","range":1,"atk":5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"sprite":"weapons:3","y":22</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"lab":"焠毒短劍",
-"des":"用毒液浸泡過的短劍，可使目標中毒"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1403,7 +1403,7 @@
         <v>138</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>162</v>
@@ -1432,16 +1432,16 @@
         <v>25</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="K13" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>79</v>
@@ -1464,7 +1464,7 @@
         <v>35</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>112</v>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -749,7 +749,7 @@
 {"stage":"hit", "scope":"target", "type":"dot",    "a":-1,        "dur":3,    "id":"poison", "icon":"🩸"},
 {"stage":"hit", "scope":"target", "type":"dot",    "m":-0.1,        "dur":3,    "id":"fire", "icon":"🔥" },
 {"stage":"hit", "scope":"self",   "type":"action", "chance":0.25, "key":"hp", "m":0.25, "id":"lifesteal"},
-{"stage":"hit", "scope":"self",   "type":"buff", "chance":0.25, "key":"str", "a":1, "dur":3, "id":"strong", "icon":"💪"}</t>
+{"stage":"hit", "scope":"self",   "type":"buff", "stack":1, "key":"str", "a":1, "dur":3, "id":"strong", "icon":"💪"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="176">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -750,6 +750,28 @@
 {"stage":"hit", "scope":"target", "type":"dot",    "m":-0.1,        "dur":3,    "id":"fire", "icon":"🔥" },
 {"stage":"hit", "scope":"self",   "type":"action", "chance":0.25, "key":"hp", "m":0.25, "id":"lifesteal"},
 {"stage":"hit", "scope":"self",   "type":"buff", "stack":1, "key":"str", "a":1, "dur":3, "id":"strong", "icon":"💪"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🔑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"鑰匙",
+"des":"可以開鎖"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"key",
+"des":""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"scale":0.5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1122,7 +1144,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr defaultColWidth="21.33203125" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17.77734375" style="3" customWidth="1"/>
@@ -1907,13 +1929,33 @@
         <v>92</v>
       </c>
     </row>
+    <row r="36" spans="1:12" ht="28.8">
+      <c r="A36" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U35">
       <formula1>$N$2:$N$13</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B35">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B36">
       <formula1>cat</formula1>
     </dataValidation>
   </dataValidations>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="183">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -753,10 +753,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>key</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>🔑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -772,6 +768,40 @@
   </si>
   <si>
     <t>"scale":0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lockpick</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAT_ITEM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🪛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab": "Lockpick",
+"des": "Used with the lockpicking skill to pick locks."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"scale":0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>key_0000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"times":3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"開鎖工具",
+"des":"開鎖的工具，需搭配開鎖技能，開鎖失敗會減少使用次數"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1144,20 +1174,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N36"/>
-  <sheetFormatPr defaultColWidth="21.33203125" defaultRowHeight="14.4"/>
+  <dimension ref="A1:N37"/>
+  <sheetFormatPr defaultColWidth="21.375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.77734375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" style="3"/>
-    <col min="3" max="3" width="15.6640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="17.75" style="3" customWidth="1"/>
+    <col min="2" max="2" width="21.375" style="3"/>
+    <col min="3" max="3" width="15.625" style="3" customWidth="1"/>
     <col min="4" max="4" width="7" style="3" customWidth="1"/>
-    <col min="5" max="5" width="48.33203125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="35.33203125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="33.88671875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="102.33203125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="72.109375" style="3" customWidth="1"/>
-    <col min="10" max="10" width="37.44140625" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="21.33203125" style="3"/>
+    <col min="5" max="5" width="48.375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="35.375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="11.75" style="3" customWidth="1"/>
+    <col min="8" max="8" width="32.75" style="3" customWidth="1"/>
+    <col min="9" max="9" width="27" style="3" customWidth="1"/>
+    <col min="10" max="10" width="37.5" style="3" customWidth="1"/>
+    <col min="11" max="11" width="21.375" style="3"/>
+    <col min="12" max="12" width="28" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="21.375" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="2" customFormat="1">
@@ -1203,7 +1235,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="28.8">
+    <row r="3" spans="1:14" ht="30">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1226,7 +1258,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="28.8">
+    <row r="4" spans="1:14" ht="30">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1252,7 +1284,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="28.8">
+    <row r="5" spans="1:14" ht="30">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -1283,7 +1315,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="28.8">
+    <row r="7" spans="1:14" ht="30">
       <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
@@ -1312,7 +1344,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="28.8">
+    <row r="8" spans="1:14" ht="30">
       <c r="A8" s="4" t="s">
         <v>21</v>
       </c>
@@ -1341,7 +1373,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="28.8">
+    <row r="9" spans="1:14" ht="30">
       <c r="A9" s="4" t="s">
         <v>22</v>
       </c>
@@ -1370,7 +1402,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="28.8">
+    <row r="10" spans="1:14" ht="30">
       <c r="A10" s="4" t="s">
         <v>23</v>
       </c>
@@ -1405,7 +1437,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="115.2">
+    <row r="12" spans="1:14" ht="120">
       <c r="A12" s="4" t="s">
         <v>24</v>
       </c>
@@ -1440,7 +1472,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="43.2">
+    <row r="13" spans="1:14" ht="45">
       <c r="A13" s="4" t="s">
         <v>25</v>
       </c>
@@ -1472,7 +1504,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="28.8">
+    <row r="14" spans="1:14" ht="30">
       <c r="A14" s="4" t="s">
         <v>26</v>
       </c>
@@ -1498,7 +1530,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="28.8">
+    <row r="15" spans="1:14" ht="30">
       <c r="A15" s="4" t="s">
         <v>64</v>
       </c>
@@ -1524,7 +1556,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="28.8">
+    <row r="16" spans="1:14" ht="30">
       <c r="A16" s="4" t="s">
         <v>65</v>
       </c>
@@ -1553,7 +1585,7 @@
     <row r="17" spans="1:12">
       <c r="A17" s="4"/>
     </row>
-    <row r="18" spans="1:12" ht="28.8">
+    <row r="18" spans="1:12" ht="30">
       <c r="A18" s="4" t="s">
         <v>27</v>
       </c>
@@ -1582,7 +1614,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="28.8">
+    <row r="19" spans="1:12" ht="30">
       <c r="A19" s="4" t="s">
         <v>28</v>
       </c>
@@ -1611,7 +1643,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="28.8">
+    <row r="20" spans="1:12" ht="30">
       <c r="A20" s="4" t="s">
         <v>29</v>
       </c>
@@ -1637,7 +1669,7 @@
     <row r="21" spans="1:12">
       <c r="A21" s="4"/>
     </row>
-    <row r="22" spans="1:12" ht="28.8">
+    <row r="22" spans="1:12" ht="30">
       <c r="A22" s="4" t="s">
         <v>30</v>
       </c>
@@ -1666,7 +1698,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="28.8">
+    <row r="23" spans="1:12" ht="30">
       <c r="A23" s="4" t="s">
         <v>31</v>
       </c>
@@ -1695,7 +1727,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="28.8">
+    <row r="24" spans="1:12" ht="30">
       <c r="A24" s="4" t="s">
         <v>32</v>
       </c>
@@ -1721,7 +1753,7 @@
     <row r="25" spans="1:12">
       <c r="A25" s="4"/>
     </row>
-    <row r="26" spans="1:12" ht="28.8">
+    <row r="26" spans="1:12" ht="30">
       <c r="A26" s="4" t="s">
         <v>33</v>
       </c>
@@ -1750,7 +1782,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="28.8">
+    <row r="27" spans="1:12" ht="30">
       <c r="A27" s="4" t="s">
         <v>61</v>
       </c>
@@ -1779,7 +1811,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="28.8">
+    <row r="28" spans="1:12" ht="30">
       <c r="A28" s="4" t="s">
         <v>34</v>
       </c>
@@ -1808,7 +1840,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="28.8">
+    <row r="29" spans="1:12" ht="30">
       <c r="A29" s="4" t="s">
         <v>56</v>
       </c>
@@ -1840,7 +1872,7 @@
     <row r="30" spans="1:12">
       <c r="A30" s="4"/>
     </row>
-    <row r="31" spans="1:12" ht="28.8">
+    <row r="31" spans="1:12" ht="30">
       <c r="A31" s="3" t="s">
         <v>35</v>
       </c>
@@ -1860,7 +1892,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="28.8">
+    <row r="32" spans="1:12" ht="30">
       <c r="A32" s="3" t="s">
         <v>36</v>
       </c>
@@ -1880,7 +1912,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="28.8">
+    <row r="34" spans="1:12" ht="30">
       <c r="A34" s="3" t="s">
         <v>37</v>
       </c>
@@ -1903,7 +1935,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="28.8">
+    <row r="35" spans="1:12" ht="30">
       <c r="A35" s="3" t="s">
         <v>38</v>
       </c>
@@ -1929,24 +1961,53 @@
         <v>92</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="28.8">
+    <row r="36" spans="1:12" ht="30">
       <c r="A36" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="3">
+        <v>10</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="K36" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="L36" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="60">
+      <c r="A37" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="K36" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>174</v>
+      <c r="B37" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D37" s="3">
+        <v>15</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -1955,7 +2016,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U35">
       <formula1>$N$2:$N$13</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B36">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B37">
       <formula1>cat</formula1>
     </dataValidation>
   </dataValidations>
@@ -1967,9 +2028,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="G13:G14"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="7" max="7" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="13" spans="7:7">
@@ -1988,7 +2049,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -1437,7 +1437,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="120">
+    <row r="12" spans="1:14" ht="300">
       <c r="A12" s="4" t="s">
         <v>24</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="45">
+    <row r="13" spans="1:14" ht="60">
       <c r="A13" s="4" t="s">
         <v>25</v>
       </c>
@@ -1504,7 +1504,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="30">
+    <row r="14" spans="1:14" ht="45">
       <c r="A14" s="4" t="s">
         <v>26</v>
       </c>
@@ -1530,7 +1530,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="30">
+    <row r="15" spans="1:14" ht="45">
       <c r="A15" s="4" t="s">
         <v>64</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="30">
+    <row r="16" spans="1:14" ht="45">
       <c r="A16" s="4" t="s">
         <v>65</v>
       </c>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="184">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -802,6 +802,10 @@
   <si>
     <t>"lab":"開鎖工具",
 "des":"開鎖的工具，需搭配開鎖技能，開鎖失敗會減少使用次數"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"cat_sub":["sword"]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1462,6 +1466,9 @@
       <c r="I12" s="3" t="s">
         <v>162</v>
       </c>
+      <c r="J12" s="3" t="s">
+        <v>183</v>
+      </c>
       <c r="K12" s="3" t="s">
         <v>115</v>
       </c>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -616,10 +616,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"endurance":360</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"useable":true,"keep":true,
 "capacity":10,"dft":3</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -806,6 +802,11 @@
   </si>
   <si>
     <t>"cat_sub":["sword"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"endurance":360,
+"light":{"color":16755200,"radius":300}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1247,7 +1248,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D3" s="3">
         <v>10</v>
@@ -1270,7 +1271,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D4" s="3">
         <v>10</v>
@@ -1296,7 +1297,7 @@
         <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D5" s="3">
         <v>10</v>
@@ -1327,13 +1328,13 @@
         <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D7" s="3">
         <v>10</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>41</v>
@@ -1356,13 +1357,13 @@
         <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D8" s="3">
         <v>15</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>42</v>
@@ -1385,13 +1386,13 @@
         <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D9" s="3">
         <v>10</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>42</v>
@@ -1414,13 +1415,13 @@
         <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D10" s="3">
         <v>15</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>43</v>
@@ -1449,25 +1450,25 @@
         <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" s="3">
         <v>15</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>138</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>115</v>
@@ -1487,22 +1488,22 @@
         <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D13" s="3">
         <v>25</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="K13" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>79</v>
@@ -1519,13 +1520,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D14" s="3">
         <v>35</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>112</v>
@@ -1545,13 +1546,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D15" s="3">
         <v>35</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>113</v>
@@ -1571,13 +1572,13 @@
         <v>9</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D16" s="3">
         <v>35</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>114</v>
@@ -1658,7 +1659,7 @@
         <v>10</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D20" s="3">
         <v>30</v>
@@ -1742,7 +1743,7 @@
         <v>11</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D24" s="3">
         <v>60</v>
@@ -1887,7 +1888,7 @@
         <v>14</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D31" s="3">
         <v>10</v>
@@ -1907,7 +1908,7 @@
         <v>15</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D32" s="3">
         <v>10</v>
@@ -1927,13 +1928,13 @@
         <v>16</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D34" s="3">
         <v>10</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>116</v>
@@ -1950,16 +1951,16 @@
         <v>19</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D35" s="3">
         <v>10</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>117</v>
@@ -1970,51 +1971,51 @@
     </row>
     <row r="36" spans="1:12" ht="30">
       <c r="A36" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D36" s="3">
         <v>10</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K36" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="L36" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="60">
       <c r="A37" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="D37" s="3">
         <v>15</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J37" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="K37" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="K37" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="L37" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -4,22 +4,24 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="equips" sheetId="1" r:id="rId1"/>
+    <sheet name="others" sheetId="2" r:id="rId2"/>
+    <sheet name="foods" sheetId="3" r:id="rId3"/>
+    <sheet name="nature" sheetId="5" r:id="rId4"/>
+    <sheet name="cat" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="cat">Sheet1!$N$2:$N$13</definedName>
+    <definedName name="cat">cat!$B$3:$B$15</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="194">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -784,10 +786,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"scale":0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>key_0000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -807,6 +805,50 @@
   <si>
     <t>"endurance":360,
 "light":{"color":16755200,"radius":300}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAT_ARMOR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAT_WEAPON</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAT_HELMET</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAT_CHESTPLATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAT_GLOVES</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAT_BOOTS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAT_NECKLACE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAT_RING</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAT_EQUIP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAT_BAG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAT_FOOD</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -814,10 +856,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="&quot;$&quot;#,##0"/>
-  </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -835,6 +874,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="微軟正黑體 Light"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="微軟正黑體 Light"/>
       <family val="2"/>
@@ -873,9 +919,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -884,6 +927,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1179,852 +1225,538 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultColWidth="21.375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.75" style="3" customWidth="1"/>
-    <col min="2" max="2" width="21.375" style="3"/>
-    <col min="3" max="3" width="15.625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="7" style="3" customWidth="1"/>
-    <col min="5" max="5" width="48.375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="35.375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="11.75" style="3" customWidth="1"/>
-    <col min="8" max="8" width="32.75" style="3" customWidth="1"/>
-    <col min="9" max="9" width="27" style="3" customWidth="1"/>
-    <col min="10" max="10" width="37.5" style="3" customWidth="1"/>
-    <col min="11" max="11" width="21.375" style="3"/>
-    <col min="12" max="12" width="28" style="3" customWidth="1"/>
-    <col min="13" max="16384" width="21.375" style="3"/>
+    <col min="1" max="1" width="11.75" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="7" style="2" customWidth="1"/>
+    <col min="5" max="5" width="48.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="35.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.75" style="2" customWidth="1"/>
+    <col min="8" max="8" width="32.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="27" style="2" customWidth="1"/>
+    <col min="10" max="10" width="37.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="21.375" style="2"/>
+    <col min="12" max="12" width="28" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="21.375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:12" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="N2" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="30">
+    <row r="3" spans="1:12" ht="300">
       <c r="A3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D3" s="3">
+        <v>24</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D3" s="2">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="60">
+      <c r="A4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4" s="2">
+        <v>25</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="45">
+      <c r="A5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D5" s="2">
+        <v>35</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="45">
+      <c r="A6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D6" s="2">
+        <v>35</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="45">
+      <c r="A7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7" s="2">
+        <v>35</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" ht="30">
+      <c r="A9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="30">
-      <c r="A4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D4" s="3">
+      <c r="C9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="2">
         <v>10</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="N4" s="3" t="s">
+      <c r="E9" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="30">
+      <c r="A10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="30">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D5" s="3">
+      <c r="C10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="2">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="30">
+      <c r="A11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="C11" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D11" s="2">
+        <v>30</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" ht="30">
+      <c r="A13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="2">
+        <v>20</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="30">
+      <c r="A14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="2">
         <v>40</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="N5" s="3" t="s">
+      <c r="E14" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="30">
+      <c r="A15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="N6" s="3" t="s">
+      <c r="C15" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D15" s="2">
+        <v>60</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="3"/>
+    </row>
+    <row r="17" spans="1:12" ht="30">
+      <c r="A17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="30">
-      <c r="A7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D7" s="3">
+      <c r="C17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="2">
         <v>10</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N7" s="3" t="s">
+      <c r="E17" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="30">
+      <c r="A18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="2">
+        <v>10</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="30">
+      <c r="A19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="30">
-      <c r="A8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D8" s="3">
+      <c r="C19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="2">
+        <v>10</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="30">
+      <c r="A20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="2">
+        <v>10</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="3"/>
+    </row>
+    <row r="22" spans="1:12" ht="30">
+      <c r="A22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D22" s="2">
+        <v>10</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="30">
+      <c r="A23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="30">
-      <c r="A9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D9" s="3">
+      <c r="C23" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D23" s="2">
         <v>10</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="30">
-      <c r="A10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D10" s="3">
-        <v>15</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="4"/>
-      <c r="N11" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="300">
-      <c r="A12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D12" s="3">
-        <v>15</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="60">
-      <c r="A13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D13" s="3">
-        <v>25</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="45">
-      <c r="A14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D14" s="3">
-        <v>35</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="45">
-      <c r="A15" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D15" s="3">
-        <v>35</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="45">
-      <c r="A16" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D16" s="3">
-        <v>35</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
-      <c r="A17" s="4"/>
-    </row>
-    <row r="18" spans="1:12" ht="30">
-      <c r="A18" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" s="3">
-        <v>10</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="30">
-      <c r="A19" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" s="3">
-        <v>20</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="30">
-      <c r="A20" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D20" s="3">
-        <v>30</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" s="4"/>
-    </row>
-    <row r="22" spans="1:12" ht="30">
-      <c r="A22" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="3">
-        <v>20</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="30">
-      <c r="A23" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="3">
-        <v>40</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="30">
-      <c r="A24" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D24" s="3">
-        <v>60</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" s="4"/>
-    </row>
-    <row r="26" spans="1:12" ht="30">
-      <c r="A26" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D26" s="3">
-        <v>10</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="30">
-      <c r="A27" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" s="3">
-        <v>10</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="30">
-      <c r="A28" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D28" s="3">
-        <v>10</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="30">
-      <c r="A29" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" s="3">
-        <v>10</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" s="4"/>
-    </row>
-    <row r="31" spans="1:12" ht="30">
-      <c r="A31" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D31" s="3">
-        <v>10</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="30">
-      <c r="A32" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D32" s="3">
-        <v>10</v>
-      </c>
-      <c r="K32" s="3" t="s">
+      <c r="K23" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="L32" s="3" t="s">
+      <c r="L23" s="2" t="s">
         <v>90</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="30">
-      <c r="A34" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D34" s="3">
-        <v>10</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="30">
-      <c r="A35" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D35" s="3">
-        <v>10</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="30">
-      <c r="A36" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D36" s="3">
-        <v>10</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="60">
-      <c r="A37" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D37" s="3">
-        <v>15</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>177</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U35">
-      <formula1>$N$2:$N$13</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B37">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B24">
       <formula1>cat</formula1>
     </dataValidation>
   </dataValidations>
@@ -2035,20 +1767,209 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G13:G14"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultColWidth="21.375" defaultRowHeight="15"/>
   <cols>
-    <col min="7" max="7" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.75" style="2" customWidth="1"/>
+    <col min="2" max="2" width="21.375" style="2"/>
+    <col min="3" max="3" width="15.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="7" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="32.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="37.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="21.375" style="2"/>
+    <col min="11" max="11" width="28" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="21.375" style="2"/>
   </cols>
   <sheetData>
-    <row r="13" spans="7:7">
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="7:7">
-      <c r="G14" s="1"/>
+    <row r="1" spans="1:11" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="30">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" s="2">
+        <v>10</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="30">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D4" s="2">
+        <v>10</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="30">
+      <c r="A6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D6" s="2">
+        <v>10</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="30">
+      <c r="A7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D7" s="2">
+        <v>10</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="30">
+      <c r="A8" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8" s="2">
+        <v>10</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="60">
+      <c r="A9" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D9" s="2">
+        <v>15</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>177</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S7">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B9">
+      <formula1>cat</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
@@ -2056,11 +1977,472 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <sheetData/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="21.375" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17.75" style="2" customWidth="1"/>
+    <col min="2" max="2" width="21.375" style="2"/>
+    <col min="3" max="3" width="15.625" style="2" customWidth="1"/>
+    <col min="4" max="5" width="7" style="2" customWidth="1"/>
+    <col min="6" max="6" width="6.5" style="2" customWidth="1"/>
+    <col min="7" max="7" width="6.375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="32.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="37.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="21.375" style="2"/>
+    <col min="11" max="11" width="28" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="21.375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="30">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" s="2">
+        <v>10</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="30">
+      <c r="A4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" s="2">
+        <v>15</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="30">
+      <c r="A5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D5" s="2">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="30">
+      <c r="A6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="2">
+        <v>15</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="30">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D8" s="2">
+        <v>10</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B6 B8">
+      <formula1>cat</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="21.375" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17.75" style="2" customWidth="1"/>
+    <col min="2" max="2" width="21.375" style="2"/>
+    <col min="3" max="3" width="15.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="6.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="7" style="2" customWidth="1"/>
+    <col min="6" max="6" width="6.5" style="2" customWidth="1"/>
+    <col min="7" max="7" width="6.375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="32.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="37.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="21.375" style="2"/>
+    <col min="11" max="11" width="28" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="21.375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="30">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" s="2">
+        <v>10</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="30">
+      <c r="A4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" s="2">
+        <v>15</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="30">
+      <c r="A5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D5" s="2">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="30">
+      <c r="A6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="2">
+        <v>15</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="30">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D8" s="2">
+        <v>10</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B6 B8">
+      <formula1>cat</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B2:B15"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="9" style="4"/>
+    <col min="2" max="2" width="21" style="4" customWidth="1"/>
+    <col min="3" max="3" width="20.375" style="4" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" s="4" customFormat="1">
+      <c r="B2" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" s="4" customFormat="1">
+      <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" s="4" customFormat="1">
+      <c r="B4" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" s="4" customFormat="1">
+      <c r="B5" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" s="4" customFormat="1">
+      <c r="B6" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" s="4" customFormat="1">
+      <c r="B7" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" s="4" customFormat="1">
+      <c r="B8" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" s="4" customFormat="1">
+      <c r="B9" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" s="4" customFormat="1">
+      <c r="B10" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" s="4" customFormat="1">
+      <c r="B11" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" s="4" customFormat="1">
+      <c r="B12" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" s="4" customFormat="1">
+      <c r="B13" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" s="4" customFormat="1">
+      <c r="B14" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" s="4" customFormat="1">
+      <c r="B15" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -4,14 +4,15 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="equips" sheetId="1" r:id="rId1"/>
     <sheet name="others" sheetId="2" r:id="rId2"/>
     <sheet name="foods" sheetId="3" r:id="rId3"/>
     <sheet name="nature" sheetId="5" r:id="rId4"/>
-    <sheet name="cat" sheetId="4" r:id="rId5"/>
+    <sheet name="resources" sheetId="6" r:id="rId5"/>
+    <sheet name="cat" sheetId="4" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="cat">cat!$B$3:$B$15</definedName>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="203">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -849,6 +850,49 @@
   </si>
   <si>
     <t>CAT_FOOD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tree</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"anchorX":0,"anchorY":48,
+"bl":10,"br":10,"bt":96,
+"gl":10,"gr":10,"gt":96,
+"zl":10,"zr":10,"zt":96,
+"isBlock":true,"weight":-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bb_view</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bb_others</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"harvest_tex":{"sprite":"assets_spritesheet_v2_free/012.png","y":40},
+"full_tex":{"sprite":"assets_spritesheet_v2_free/001.png"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wood</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Wood",
+"des":""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"木材",
+"des":"有用的資源"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets_spritesheet_v2_free/028.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2169,18 +2213,80 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultColWidth="21.375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.75" style="2" customWidth="1"/>
     <col min="2" max="2" width="21.375" style="2"/>
     <col min="3" max="3" width="15.625" style="2" customWidth="1"/>
     <col min="4" max="4" width="6.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.5" style="2" customWidth="1"/>
+    <col min="7" max="7" width="44.875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="21.375" style="2"/>
+    <col min="9" max="9" width="28" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="21.375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="75">
+      <c r="A3" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultColWidth="21.375" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17.75" style="2" customWidth="1"/>
+    <col min="2" max="2" width="21.375" style="2"/>
+    <col min="3" max="3" width="33.125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="6" style="2" customWidth="1"/>
     <col min="5" max="5" width="7" style="2" customWidth="1"/>
-    <col min="6" max="6" width="6.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.75" style="2" customWidth="1"/>
     <col min="7" max="7" width="6.375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="32.75" style="2" customWidth="1"/>
-    <col min="9" max="9" width="37.5" style="2" customWidth="1"/>
+    <col min="8" max="9" width="8.125" style="2" customWidth="1"/>
     <col min="10" max="10" width="21.375" style="2"/>
     <col min="11" max="11" width="28" style="2" customWidth="1"/>
     <col min="12" max="16384" width="21.375" style="2"/>
@@ -2223,130 +2329,32 @@
     </row>
     <row r="3" spans="1:11" ht="30">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>199</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>143</v>
+        <v>202</v>
       </c>
       <c r="D3" s="2">
-        <v>10</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>125</v>
+        <v>201</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="30">
-      <c r="A4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D4" s="2">
-        <v>15</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="30">
-      <c r="A5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D5" s="2">
-        <v>10</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="30">
-      <c r="A6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D6" s="2">
-        <v>15</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="30">
-      <c r="A8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D8" s="2">
-        <v>10</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>71</v>
-      </c>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2359,7 +2367,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="B2:B15"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
@@ -2370,72 +2378,72 @@
     <col min="4" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" s="4" customFormat="1">
+    <row r="2" spans="2:2">
       <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:2" s="4" customFormat="1">
+    <row r="3" spans="2:2">
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:2" s="4" customFormat="1">
+    <row r="4" spans="2:2">
       <c r="B4" s="4" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="5" spans="2:2" s="4" customFormat="1">
+    <row r="5" spans="2:2">
       <c r="B5" s="4" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="6" spans="2:2" s="4" customFormat="1">
+    <row r="6" spans="2:2">
       <c r="B6" s="4" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="7" spans="2:2" s="4" customFormat="1">
+    <row r="7" spans="2:2">
       <c r="B7" s="4" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="8" spans="2:2" s="4" customFormat="1">
+    <row r="8" spans="2:2">
       <c r="B8" s="4" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="9" spans="2:2" s="4" customFormat="1">
+    <row r="9" spans="2:2">
       <c r="B9" s="4" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="10" spans="2:2" s="4" customFormat="1">
+    <row r="10" spans="2:2">
       <c r="B10" s="4" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="11" spans="2:2" s="4" customFormat="1">
+    <row r="11" spans="2:2">
       <c r="B11" s="4" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="12" spans="2:2" s="4" customFormat="1">
+    <row r="12" spans="2:2">
       <c r="B12" s="4" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="13" spans="2:2" s="4" customFormat="1">
+    <row r="13" spans="2:2">
       <c r="B13" s="4" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="14" spans="2:2" s="4" customFormat="1">
+    <row r="14" spans="2:2">
       <c r="B14" s="4" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="15" spans="2:2" s="4" customFormat="1">
+    <row r="15" spans="2:2">
       <c r="B15" s="4" t="s">
         <v>175</v>
       </c>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="equips" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="204">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -873,11 +873,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"harvest_tex":{"sprite":"assets_spritesheet_v2_free/012.png","y":40},
-"full_tex":{"sprite":"assets_spritesheet_v2_free/001.png"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>wood</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -893,6 +888,16 @@
   </si>
   <si>
     <t>assets_spritesheet_v2_free/028.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"cps":10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"harvest_tex":{"sprite":"assets_spritesheet_v2_free/012.png","y":40},
+"full_tex":{"sprite":"assets_spritesheet_v2_free/001.png"},
+"harvest":{"id":"wood","count":1,"drop":true}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2217,12 +2222,12 @@
   <sheetFormatPr defaultColWidth="21.375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.75" style="2" customWidth="1"/>
-    <col min="2" max="2" width="21.375" style="2"/>
-    <col min="3" max="3" width="15.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.25" style="2" customWidth="1"/>
     <col min="4" max="4" width="6.25" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11.5" style="2" customWidth="1"/>
-    <col min="7" max="7" width="44.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.5" style="2" customWidth="1"/>
+    <col min="7" max="7" width="55.5" style="2" customWidth="1"/>
     <col min="8" max="8" width="21.375" style="2"/>
     <col min="9" max="9" width="28" style="2" customWidth="1"/>
     <col min="10" max="16384" width="21.375" style="2"/>
@@ -2265,7 +2270,7 @@
         <v>195</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -2286,7 +2291,8 @@
     <col min="5" max="5" width="7" style="2" customWidth="1"/>
     <col min="6" max="6" width="9.75" style="2" customWidth="1"/>
     <col min="7" max="7" width="6.375" style="2" customWidth="1"/>
-    <col min="8" max="9" width="8.125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.75" style="2" customWidth="1"/>
     <col min="10" max="10" width="21.375" style="2"/>
     <col min="11" max="11" width="28" style="2" customWidth="1"/>
     <col min="12" max="16384" width="21.375" style="2"/>
@@ -2329,22 +2335,25 @@
     </row>
     <row r="3" spans="1:11" ht="30">
       <c r="A3" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
       </c>
+      <c r="I3" s="2" t="s">
+        <v>202</v>
+      </c>
       <c r="J3" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:11">

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="equips" sheetId="1" r:id="rId1"/>
@@ -93,10 +93,6 @@
     <t>CAT_ITEM</t>
   </si>
   <si>
-    <t>others</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>cooked_meat</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -568,10 +564,6 @@
   <si>
     <t>"lab":"熟肉",
 "des":"熟肉"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>meta</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -898,6 +890,14 @@
     <t>"harvest_tex":{"sprite":"assets_spritesheet_v2_free/012.png","y":40},
 "full_tex":{"sprite":"assets_spritesheet_v2_free/001.png"},
 "harvest":{"id":"wood","count":1,"drop":true}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_others</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_meta</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1306,170 +1306,170 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>127</v>
+        <v>203</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>20</v>
+        <v>202</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="300">
       <c r="A3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D3" s="2">
         <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="60">
       <c r="A4" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D4" s="2">
         <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="L4" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="45">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D5" s="2">
         <v>35</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="45">
       <c r="A6" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D6" s="2">
         <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K6" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="45">
       <c r="A7" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D7" s="2">
         <v>35</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1477,83 +1477,83 @@
     </row>
     <row r="9" spans="1:12" ht="30">
       <c r="A9" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D9" s="2">
         <v>10</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="30">
       <c r="A10" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D10" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="30">
       <c r="A11" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D11" s="2">
         <v>30</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1561,83 +1561,83 @@
     </row>
     <row r="13" spans="1:12" ht="30">
       <c r="A13" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D13" s="2">
         <v>20</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="30">
       <c r="A14" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" s="2">
         <v>40</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="30">
       <c r="A15" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D15" s="2">
         <v>60</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1645,118 +1645,118 @@
     </row>
     <row r="17" spans="1:12" ht="30">
       <c r="A17" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D17" s="2">
         <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="30">
       <c r="A18" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D18" s="2">
         <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="30">
       <c r="A19" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D19" s="2">
         <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="30">
       <c r="A20" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D20" s="2">
         <v>10</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1764,42 +1764,42 @@
     </row>
     <row r="22" spans="1:12" ht="30">
       <c r="A22" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D22" s="2">
         <v>10</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="30">
       <c r="A23" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D23" s="2">
         <v>10</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1847,25 +1847,25 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>127</v>
+        <v>203</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>20</v>
+        <v>202</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30">
@@ -1876,16 +1876,16 @@
         <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D3" s="2">
         <v>10</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30">
@@ -1896,117 +1896,117 @@
         <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D4" s="2">
         <v>10</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="30">
       <c r="A6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D6" s="2">
         <v>10</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="30">
       <c r="A7" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D7" s="2">
         <v>10</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="30">
       <c r="A8" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D8" s="2">
         <v>10</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="60">
       <c r="A9" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="D9" s="2">
         <v>15</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -2056,25 +2056,25 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>127</v>
+        <v>203</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>20</v>
+        <v>202</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30">
@@ -2085,100 +2085,100 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D3" s="2">
         <v>10</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30">
       <c r="A4" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D4" s="2">
         <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="30">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D5" s="2">
         <v>10</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="30">
       <c r="A6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D6" s="2">
         <v>15</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="30">
@@ -2189,19 +2189,19 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D8" s="2">
         <v>10</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -2247,30 +2247,30 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>127</v>
+        <v>203</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="75">
       <c r="A3" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -2312,48 +2312,48 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>127</v>
+        <v>203</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>20</v>
+        <v>202</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30">
       <c r="A3" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2399,62 +2399,62 @@
     </row>
     <row r="4" spans="2:2">
       <c r="B4" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="2:2">
       <c r="B11" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="equips" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="217">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -616,34 +616,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>icons:273</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:250</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:137</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:241</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:242</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:259</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:260</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>weapons:3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -669,22 +641,6 @@
   </si>
   <si>
     <t>weapons:56</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:134</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:132</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:170</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:307</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -898,6 +854,110 @@
   </si>
   <si>
     <t>_meta</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>appletree</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"harvest_tex":{"sprite":"assets_spritesheet_v2_free/005.png"},
+"full_tex":{"sprite":"assets_spritesheet_v2_free/006.png"},
+"harvest":{"id":"apple","count":1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>apple</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Apple",
+"des":""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"頻果",
+"des":"可食用"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:necklace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:ring</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:torch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:bag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:iron</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:bottle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:raw_meat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:cooked_meat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:raw_fish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:salt_baked_fish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:salt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:apple</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"葡萄",
+"des":"可食用"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Strawberry",
+"des":""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"cps":5,"useable":true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grapes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grapetree</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"harvest_tex":{"sprite":"assets_spritesheet_v2_free/011.png"},
+"full_tex":{"sprite":"assets_spritesheet_v2_free/010.png"},
+"harvest":{"id":"grapes","count":1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:grapes</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1312,7 +1372,7 @@
         <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>134</v>
@@ -1321,7 +1381,7 @@
         <v>135</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>65</v>
@@ -1338,25 +1398,25 @@
         <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D3" s="2">
         <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>136</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>114</v>
@@ -1373,22 +1433,22 @@
         <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D4" s="2">
         <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>78</v>
@@ -1402,13 +1462,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D5" s="2">
         <v>35</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>111</v>
@@ -1428,13 +1488,13 @@
         <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D6" s="2">
         <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>112</v>
@@ -1454,13 +1514,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D7" s="2">
         <v>35</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>113</v>
@@ -1541,7 +1601,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D11" s="2">
         <v>30</v>
@@ -1625,7 +1685,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D15" s="2">
         <v>60</v>
@@ -1770,7 +1830,7 @@
         <v>14</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>152</v>
+        <v>198</v>
       </c>
       <c r="D22" s="2">
         <v>10</v>
@@ -1790,7 +1850,7 @@
         <v>15</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="D23" s="2">
         <v>10</v>
@@ -1853,13 +1913,13 @@
         <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>65</v>
@@ -1876,7 +1936,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>138</v>
+        <v>202</v>
       </c>
       <c r="D3" s="2">
         <v>10</v>
@@ -1896,7 +1956,7 @@
         <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>140</v>
+        <v>201</v>
       </c>
       <c r="D4" s="2">
         <v>10</v>
@@ -1919,13 +1979,13 @@
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>154</v>
+        <v>200</v>
       </c>
       <c r="D6" s="2">
         <v>10</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>115</v>
@@ -1942,13 +2002,13 @@
         <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>155</v>
+        <v>203</v>
       </c>
       <c r="D7" s="2">
         <v>10</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>137</v>
@@ -1962,51 +2022,51 @@
     </row>
     <row r="8" spans="1:11" ht="30">
       <c r="A8" s="2" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="D8" s="2">
         <v>10</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="60">
       <c r="A9" s="2" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="D9" s="2">
         <v>15</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -2026,12 +2086,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultColWidth="21.375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.75" style="2" customWidth="1"/>
     <col min="2" max="2" width="21.375" style="2"/>
-    <col min="3" max="3" width="15.625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.625" style="2" customWidth="1"/>
     <col min="4" max="5" width="7" style="2" customWidth="1"/>
     <col min="6" max="6" width="6.5" style="2" customWidth="1"/>
     <col min="7" max="7" width="6.375" style="2" customWidth="1"/>
@@ -2062,13 +2122,13 @@
         <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>65</v>
@@ -2085,13 +2145,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>141</v>
+        <v>204</v>
       </c>
       <c r="D3" s="2">
         <v>10</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>40</v>
@@ -2111,13 +2171,13 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>142</v>
+        <v>205</v>
       </c>
       <c r="D4" s="2">
         <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>41</v>
@@ -2137,13 +2197,13 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>143</v>
+        <v>206</v>
       </c>
       <c r="D5" s="2">
         <v>10</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>41</v>
@@ -2163,13 +2223,13 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>144</v>
+        <v>207</v>
       </c>
       <c r="D6" s="2">
         <v>15</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>42</v>
@@ -2189,7 +2249,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>139</v>
+        <v>208</v>
       </c>
       <c r="D8" s="2">
         <v>10</v>
@@ -2202,12 +2262,64 @@
       </c>
       <c r="K8" s="2" t="s">
         <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="30">
+      <c r="A10" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D10" s="2">
+        <v>10</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="30">
+      <c r="A11" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D11" s="2">
+        <v>10</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>211</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B6 B8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B6 B8 B10:B11">
       <formula1>cat</formula1>
     </dataValidation>
   </dataValidations>
@@ -2218,7 +2330,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultColWidth="21.375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.75" style="2" customWidth="1"/>
@@ -2227,7 +2339,7 @@
     <col min="4" max="4" width="6.25" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.5" style="2" customWidth="1"/>
     <col min="6" max="6" width="10.5" style="2" customWidth="1"/>
-    <col min="7" max="7" width="55.5" style="2" customWidth="1"/>
+    <col min="7" max="7" width="57.625" style="2" customWidth="1"/>
     <col min="8" max="8" width="21.375" style="2"/>
     <col min="9" max="9" width="28" style="2" customWidth="1"/>
     <col min="10" max="16384" width="21.375" style="2"/>
@@ -2247,13 +2359,13 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>65</v>
@@ -2264,13 +2376,29 @@
     </row>
     <row r="3" spans="1:9" ht="75">
       <c r="A3" s="2" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="45">
+      <c r="A4" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>201</v>
+      <c r="G4" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="45">
+      <c r="A5" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -2289,7 +2417,7 @@
     <col min="3" max="3" width="33.125" style="2" customWidth="1"/>
     <col min="4" max="4" width="6" style="2" customWidth="1"/>
     <col min="5" max="5" width="7" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="2" customWidth="1"/>
     <col min="7" max="7" width="6.375" style="2" customWidth="1"/>
     <col min="8" max="8" width="8.125" style="2" customWidth="1"/>
     <col min="9" max="9" width="10.75" style="2" customWidth="1"/>
@@ -2318,13 +2446,13 @@
         <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>65</v>
@@ -2335,25 +2463,25 @@
     </row>
     <row r="3" spans="1:11" ht="30">
       <c r="A3" s="3" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2399,62 +2527,62 @@
     </row>
     <row r="4" spans="2:2">
       <c r="B4" s="4" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" s="4" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" s="4" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" s="4" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" s="4" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" s="4" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" s="4" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="2:2">
       <c r="B11" s="4" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" s="4" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" s="4" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" s="4" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" s="4" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="equips" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="224">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -843,121 +843,156 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"harvest_tex":{"sprite":"assets_spritesheet_v2_free/012.png","y":40},
+    <t>_others</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_meta</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>appletree</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>apple</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Apple",
+"des":""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"頻果",
+"des":"可食用"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:necklace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:ring</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:torch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:bag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:iron</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:bottle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:raw_meat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:cooked_meat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:raw_fish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:salt_baked_fish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:salt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:apple</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"葡萄",
+"des":"可食用"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Strawberry",
+"des":""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"cps":5,"useable":true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grapes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grapetree</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:grapes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"act":"harvest",
+"harvest_tex":{"sprite":"assets_spritesheet_v2_free/005.png"},
+"full_tex":{"sprite":"assets_spritesheet_v2_free/006.png"},
+"harvest":{"id":"apple","count":3}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"act":"harvest",
+"harvest_tex":{"sprite":"assets_spritesheet_v2_free/011.png"},
+"full_tex":{"sprite":"assets_spritesheet_v2_free/010.png"},
+"harvest":{"id":"grapes","count":3}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mushtree</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"act":"harvest",
+"full_tex":{"sprite":"assets_spritesheet_v2_free/034.png"},
+"harvest":{"id":"mushroom","count":1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mushroom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"act":"chop","chopCnt": 3,
+"harvest_tex":{"sprite":"assets_spritesheet_v2_free/012.png","y":40},
 "full_tex":{"sprite":"assets_spritesheet_v2_free/001.png"},
 "harvest":{"id":"wood","count":1,"drop":true}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>_others</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>_meta</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>appletree</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"harvest_tex":{"sprite":"assets_spritesheet_v2_free/005.png"},
-"full_tex":{"sprite":"assets_spritesheet_v2_free/006.png"},
-"harvest":{"id":"apple","count":1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>apple</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"lab":"Apple",
-"des":""</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"lab":"頻果",
+    <t>"cps":10,"useable":true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Mushroom",
+"des":""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"蘑菇",
 "des":"可食用"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>icons:necklace</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:ring</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:torch</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:bag</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:iron</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:bottle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:raw_meat</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:cooked_meat</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:raw_fish</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:salt_baked_fish</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:salt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:apple</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"lab":"葡萄",
-"des":"可食用"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"lab":"Strawberry",
-"des":""</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"cps":5,"useable":true</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>grapes</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>grapetree</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"harvest_tex":{"sprite":"assets_spritesheet_v2_free/011.png"},
-"full_tex":{"sprite":"assets_spritesheet_v2_free/010.png"},
-"harvest":{"id":"grapes","count":1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:grapes</t>
+    <t>icons:mushroom</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1372,7 +1407,7 @@
         <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>134</v>
@@ -1381,7 +1416,7 @@
         <v>135</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>65</v>
@@ -1830,7 +1865,7 @@
         <v>14</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D22" s="2">
         <v>10</v>
@@ -1850,7 +1885,7 @@
         <v>15</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D23" s="2">
         <v>10</v>
@@ -1913,13 +1948,13 @@
         <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>65</v>
@@ -1936,7 +1971,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D3" s="2">
         <v>10</v>
@@ -1956,7 +1991,7 @@
         <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D4" s="2">
         <v>10</v>
@@ -1979,7 +2014,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D6" s="2">
         <v>10</v>
@@ -2002,7 +2037,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D7" s="2">
         <v>10</v>
@@ -2086,7 +2121,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultColWidth="21.375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.75" style="2" customWidth="1"/>
@@ -2122,13 +2157,13 @@
         <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>65</v>
@@ -2145,7 +2180,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D3" s="2">
         <v>10</v>
@@ -2171,7 +2206,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D4" s="2">
         <v>15</v>
@@ -2197,7 +2232,7 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D5" s="2">
         <v>10</v>
@@ -2223,7 +2258,7 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D6" s="2">
         <v>15</v>
@@ -2249,7 +2284,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D8" s="2">
         <v>10</v>
@@ -2266,13 +2301,13 @@
     </row>
     <row r="10" spans="1:11" ht="30">
       <c r="A10" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D10" s="2">
         <v>10</v>
@@ -2281,24 +2316,24 @@
         <v>149</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="30">
       <c r="A11" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D11" s="2">
         <v>10</v>
@@ -2307,19 +2342,45 @@
         <v>149</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="30">
+      <c r="A12" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D12" s="2">
+        <v>5</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B6 B8 B10:B11">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B6 B8 B10:B12">
       <formula1>cat</formula1>
     </dataValidation>
   </dataValidations>
@@ -2330,7 +2391,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultColWidth="21.375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.75" style="2" customWidth="1"/>
@@ -2362,7 +2423,7 @@
         <v>183</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>184</v>
@@ -2382,23 +2443,31 @@
         <v>182</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="45">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="60">
       <c r="A4" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="45">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="60">
       <c r="A5" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>215</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="45">
+      <c r="A6" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -2446,13 +2515,13 @@
         <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>65</v>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="equips" sheetId="1" r:id="rId1"/>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="equips" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="229">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -971,28 +971,50 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"act":"chop","chopCnt": 3,
+    <t>"cps":10,"useable":true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Mushroom",
+"des":""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"蘑菇",
+"des":"可食用"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:mushroom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>axe_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Axe",
+"des":""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"act":"chop","chopCnt": 3,"tool":"axe",
 "harvest_tex":{"sprite":"assets_spritesheet_v2_free/012.png","y":40},
 "full_tex":{"sprite":"assets_spritesheet_v2_free/001.png"},
 "harvest":{"id":"wood","count":1,"drop":true}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"cps":10,"useable":true</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"lab":"Mushroom",
-"des":""</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"lab":"蘑菇",
-"des":"可食用"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:mushroom</t>
+    <t>weapons:6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"斧頭",
+"des":""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"cat_sub":["axe"]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1369,7 +1391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultColWidth="21.375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.75" style="2" customWidth="1"/>
@@ -1378,7 +1400,7 @@
     <col min="4" max="4" width="7" style="2" customWidth="1"/>
     <col min="5" max="5" width="48.375" style="2" customWidth="1"/>
     <col min="6" max="6" width="35.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.75" style="2" customWidth="1"/>
+    <col min="7" max="7" width="28.625" style="2" customWidth="1"/>
     <col min="8" max="8" width="32.75" style="2" customWidth="1"/>
     <col min="9" max="9" width="27" style="2" customWidth="1"/>
     <col min="10" max="10" width="37.5" style="2" customWidth="1"/>
@@ -1897,10 +1919,39 @@
         <v>89</v>
       </c>
     </row>
+    <row r="26" spans="1:12" ht="30">
+      <c r="A26" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D26" s="2">
+        <v>10</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B23 B26">
       <formula1>cat</formula1>
     </dataValidation>
   </dataValidations>
@@ -2359,7 +2410,7 @@
         <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D12" s="2">
         <v>5</v>
@@ -2368,13 +2419,13 @@
         <v>149</v>
       </c>
       <c r="I12" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -2443,7 +2494,7 @@
         <v>182</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="60">

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -4,15 +4,16 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="equips" sheetId="1" r:id="rId1"/>
     <sheet name="others" sheetId="2" r:id="rId2"/>
     <sheet name="foods" sheetId="3" r:id="rId3"/>
-    <sheet name="nature" sheetId="5" r:id="rId4"/>
-    <sheet name="resources" sheetId="6" r:id="rId5"/>
-    <sheet name="cat" sheetId="4" r:id="rId6"/>
+    <sheet name="dev" sheetId="8" r:id="rId4"/>
+    <sheet name="nature" sheetId="5" r:id="rId5"/>
+    <sheet name="resources" sheetId="6" r:id="rId6"/>
+    <sheet name="cat" sheetId="4" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="cat">cat!$B$3:$B$15</definedName>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="236">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -869,54 +870,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>icons:necklace</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:ring</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:torch</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:bag</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:iron</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:bottle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:raw_meat</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:cooked_meat</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:raw_fish</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:salt_baked_fish</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:salt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:apple</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"lab":"葡萄",
 "des":"可食用"</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -936,10 +889,6 @@
   </si>
   <si>
     <t>grapetree</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:grapes</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -961,12 +910,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"act":"harvest",
-"full_tex":{"sprite":"assets_spritesheet_v2_free/034.png"},
-"harvest":{"id":"mushroom","count":1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>mushroom</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -982,10 +925,6 @@
   <si>
     <t>"lab":"蘑菇",
 "des":"可食用"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icons:mushroom</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1015,6 +954,98 @@
   </si>
   <si>
     <t>"cat_sub":["axe"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab": "Pot",
+"des": ""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"鍋子",
+"des":"可烹煮食物"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dev_pot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"class":"pot"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"device":"dev_pot"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:134</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:132</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:273</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:237</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:170</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:307</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:241</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:242</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:259</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:260</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:224</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:229</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:236</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:313</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"act":"harvest",
+"full_tex":{"sprite":"icons:236"},
+"harvest":{"id":"mushroom","count":1}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1887,7 +1918,7 @@
         <v>14</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="D22" s="2">
         <v>10</v>
@@ -1907,7 +1938,7 @@
         <v>15</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="D23" s="2">
         <v>10</v>
@@ -1921,13 +1952,13 @@
     </row>
     <row r="26" spans="1:12" ht="30">
       <c r="A26" s="2" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="D26" s="2">
         <v>10</v>
@@ -1939,13 +1970,13 @@
         <v>136</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -1962,7 +1993,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultColWidth="21.375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.75" style="2" customWidth="1"/>
@@ -2022,7 +2053,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="D3" s="2">
         <v>10</v>
@@ -2042,7 +2073,7 @@
         <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="D4" s="2">
         <v>10</v>
@@ -2065,7 +2096,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="D6" s="2">
         <v>10</v>
@@ -2088,7 +2119,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="D7" s="2">
         <v>10</v>
@@ -2153,6 +2184,29 @@
       </c>
       <c r="K9" s="2" t="s">
         <v>164</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="30">
+      <c r="A11" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D11" s="2">
+        <v>100</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -2161,7 +2215,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S7">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B9 B11">
       <formula1>cat</formula1>
     </dataValidation>
   </dataValidations>
@@ -2231,7 +2285,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="D3" s="2">
         <v>10</v>
@@ -2257,7 +2311,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="D4" s="2">
         <v>15</v>
@@ -2283,7 +2337,7 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="D5" s="2">
         <v>10</v>
@@ -2309,7 +2363,7 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="D6" s="2">
         <v>15</v>
@@ -2335,7 +2389,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="D8" s="2">
         <v>10</v>
@@ -2358,7 +2412,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="D10" s="2">
         <v>10</v>
@@ -2367,7 +2421,7 @@
         <v>149</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>195</v>
@@ -2378,13 +2432,13 @@
     </row>
     <row r="11" spans="1:11" ht="30">
       <c r="A11" s="2" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="D11" s="2">
         <v>10</v>
@@ -2393,24 +2447,24 @@
         <v>149</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="30">
       <c r="A12" s="2" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="D12" s="2">
         <v>5</v>
@@ -2419,13 +2473,13 @@
         <v>149</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -2441,6 +2495,66 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="2" max="2" width="12.625" customWidth="1"/>
+    <col min="6" max="6" width="22.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3">
+      <formula1>cat</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultColWidth="21.375" defaultRowHeight="15"/>
@@ -2494,7 +2608,7 @@
         <v>182</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="60">
@@ -2502,23 +2616,23 @@
         <v>192</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="60">
       <c r="A5" s="2" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="45">
       <c r="A6" s="2" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -2527,7 +2641,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="21.375" defaultRowHeight="15"/>
@@ -2624,7 +2738,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="B2:B15"/>
   <sheetFormatPr defaultRowHeight="15.75"/>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="equips" sheetId="1" r:id="rId1"/>
@@ -16,14 +16,14 @@
     <sheet name="cat" sheetId="4" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="cat">cat!$B$3:$B$15</definedName>
+    <definedName name="cat">cat!$B$3:$B$16</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="238">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1046,6 +1046,13 @@
     <t>"act":"harvest",
 "full_tex":{"sprite":"icons:236"},
 "harvest":{"id":"mushroom","count":1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAT_DEVICE</t>
+  </si>
+  <si>
+    <t>CAT_DEVICE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1542,7 +1549,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="45">
+    <row r="5" spans="1:12" ht="30">
       <c r="A5" s="3" t="s">
         <v>25</v>
       </c>
@@ -1568,7 +1575,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="45">
+    <row r="6" spans="1:12" ht="30">
       <c r="A6" s="3" t="s">
         <v>63</v>
       </c>
@@ -1594,7 +1601,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="45">
+    <row r="7" spans="1:12" ht="30">
       <c r="A7" s="3" t="s">
         <v>64</v>
       </c>
@@ -2191,7 +2198,7 @@
         <v>216</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>162</v>
+        <v>236</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>234</v>
@@ -2503,7 +2510,7 @@
     <col min="6" max="6" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="15">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2537,7 +2544,7 @@
         <v>217</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>236</v>
       </c>
       <c r="F3" t="s">
         <v>218</v>
@@ -2740,7 +2747,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:B15"/>
+  <dimension ref="B2:B16"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -2819,6 +2826,11 @@
         <v>162</v>
       </c>
     </row>
+    <row r="16" spans="2:2">
+      <c r="B16" s="4" t="s">
+        <v>237</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="equips" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="239">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -979,10 +979,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"device":"dev_pot"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>icons:134</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1053,6 +1049,14 @@
   </si>
   <si>
     <t>CAT_DEVICE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"device":{"class":"stove"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"wid":32,"hei":32</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1925,7 +1929,7 @@
         <v>14</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D22" s="2">
         <v>10</v>
@@ -1945,7 +1949,7 @@
         <v>15</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D23" s="2">
         <v>10</v>
@@ -2060,7 +2064,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D3" s="2">
         <v>10</v>
@@ -2080,7 +2084,7 @@
         <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D4" s="2">
         <v>10</v>
@@ -2103,7 +2107,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D6" s="2">
         <v>10</v>
@@ -2126,7 +2130,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D7" s="2">
         <v>10</v>
@@ -2198,16 +2202,16 @@
         <v>216</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D11" s="2">
         <v>100</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>215</v>
@@ -2292,7 +2296,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D3" s="2">
         <v>10</v>
@@ -2318,7 +2322,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D4" s="2">
         <v>15</v>
@@ -2344,7 +2348,7 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D5" s="2">
         <v>10</v>
@@ -2370,7 +2374,7 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D6" s="2">
         <v>15</v>
@@ -2396,7 +2400,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D8" s="2">
         <v>10</v>
@@ -2419,7 +2423,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D10" s="2">
         <v>10</v>
@@ -2445,7 +2449,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D11" s="2">
         <v>10</v>
@@ -2471,7 +2475,7 @@
         <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D12" s="2">
         <v>5</v>
@@ -2508,9 +2512,10 @@
   <cols>
     <col min="2" max="2" width="12.625" customWidth="1"/>
     <col min="6" max="6" width="22.5" customWidth="1"/>
+    <col min="7" max="7" width="23.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="30">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2543,11 +2548,12 @@
       <c r="A3" t="s">
         <v>217</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>236</v>
-      </c>
+      <c r="B3" s="2"/>
       <c r="F3" t="s">
         <v>218</v>
+      </c>
+      <c r="G3" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -2639,7 +2645,7 @@
         <v>203</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2828,7 +2834,7 @@
     </row>
     <row r="16" spans="2:2">
       <c r="B16" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="equips" sheetId="1" r:id="rId1"/>
@@ -975,10 +975,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"class":"pot"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>icons:134</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1052,11 +1048,16 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"device":{"class":"stove"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"wid":32,"hei":32</t>
+    <t>"wid":32,"hei":32,
+"key":"icons","frame":"313"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"class":"stove"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"device":{"class":"stove","id":"dev_pot"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1123,7 +1124,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1138,6 +1139,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1929,7 +1933,7 @@
         <v>14</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D22" s="2">
         <v>10</v>
@@ -1949,7 +1953,7 @@
         <v>15</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D23" s="2">
         <v>10</v>
@@ -2064,7 +2068,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D3" s="2">
         <v>10</v>
@@ -2084,7 +2088,7 @@
         <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D4" s="2">
         <v>10</v>
@@ -2107,7 +2111,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D6" s="2">
         <v>10</v>
@@ -2130,7 +2134,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D7" s="2">
         <v>10</v>
@@ -2202,16 +2206,16 @@
         <v>216</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D11" s="2">
         <v>100</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>215</v>
@@ -2296,7 +2300,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D3" s="2">
         <v>10</v>
@@ -2322,7 +2326,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D4" s="2">
         <v>15</v>
@@ -2348,7 +2352,7 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D5" s="2">
         <v>10</v>
@@ -2374,7 +2378,7 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D6" s="2">
         <v>15</v>
@@ -2400,7 +2404,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D8" s="2">
         <v>10</v>
@@ -2423,7 +2427,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D10" s="2">
         <v>10</v>
@@ -2449,7 +2453,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D11" s="2">
         <v>10</v>
@@ -2475,7 +2479,7 @@
         <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D12" s="2">
         <v>5</v>
@@ -2511,6 +2515,7 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="12.625" customWidth="1"/>
+    <col min="5" max="5" width="30.625" customWidth="1"/>
     <col min="6" max="6" width="22.5" customWidth="1"/>
     <col min="7" max="7" width="23.75" customWidth="1"/>
   </cols>
@@ -2544,16 +2549,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" ht="33">
       <c r="A3" t="s">
         <v>217</v>
       </c>
       <c r="B3" s="2"/>
+      <c r="E3" s="5" t="s">
+        <v>236</v>
+      </c>
       <c r="F3" t="s">
-        <v>218</v>
-      </c>
-      <c r="G3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -2645,7 +2650,7 @@
         <v>203</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -2834,7 +2839,7 @@
     </row>
     <row r="16" spans="2:2">
       <c r="B16" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="equips" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="238">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1053,11 +1053,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"class":"stove"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"device":{"class":"stove","id":"dev_pot"}</t>
+    <t>"device":{"class":"pot","id":"dev_pot"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2215,7 +2211,7 @@
         <v>100</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>215</v>
@@ -2557,9 +2553,6 @@
       <c r="E3" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="F3" t="s">
-        <v>237</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="7290" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="equips" sheetId="1" r:id="rId1"/>
     <sheet name="others" sheetId="2" r:id="rId2"/>
     <sheet name="foods" sheetId="3" r:id="rId3"/>
-    <sheet name="dev" sheetId="8" r:id="rId4"/>
+    <sheet name="device" sheetId="8" r:id="rId4"/>
     <sheet name="nature" sheetId="5" r:id="rId5"/>
     <sheet name="resources" sheetId="6" r:id="rId6"/>
     <sheet name="cat" sheetId="4" r:id="rId7"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="238">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -971,10 +971,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dev_pot</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>icons:134</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1048,12 +1044,16 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>_others</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"device":{"class":"pot"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>"wid":32,"hei":32,
-"key":"icons","frame":"313"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"device":{"class":"pot","id":"dev_pot"}</t>
+"key":"icons","frame":"312"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1929,7 +1929,7 @@
         <v>14</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D22" s="2">
         <v>10</v>
@@ -1949,7 +1949,7 @@
         <v>15</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D23" s="2">
         <v>10</v>
@@ -2004,7 +2004,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultColWidth="21.375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.75" style="2" customWidth="1"/>
@@ -2064,7 +2064,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D3" s="2">
         <v>10</v>
@@ -2084,7 +2084,7 @@
         <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D4" s="2">
         <v>10</v>
@@ -2107,7 +2107,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D6" s="2">
         <v>10</v>
@@ -2130,7 +2130,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D7" s="2">
         <v>10</v>
@@ -2195,29 +2195,6 @@
       </c>
       <c r="K9" s="2" t="s">
         <v>164</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="30">
-      <c r="A11" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D11" s="2">
-        <v>100</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -2226,7 +2203,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S7">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B9 B11">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B9">
       <formula1>cat</formula1>
     </dataValidation>
   </dataValidations>
@@ -2296,7 +2273,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D3" s="2">
         <v>10</v>
@@ -2322,7 +2299,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D4" s="2">
         <v>15</v>
@@ -2348,7 +2325,7 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D5" s="2">
         <v>10</v>
@@ -2374,7 +2351,7 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D6" s="2">
         <v>15</v>
@@ -2400,7 +2377,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D8" s="2">
         <v>10</v>
@@ -2423,7 +2400,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D10" s="2">
         <v>10</v>
@@ -2449,7 +2426,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D11" s="2">
         <v>10</v>
@@ -2475,7 +2452,7 @@
         <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D12" s="2">
         <v>5</v>
@@ -2507,16 +2484,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="12.625" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="30.625" customWidth="1"/>
-    <col min="6" max="6" width="22.5" customWidth="1"/>
-    <col min="7" max="7" width="23.75" customWidth="1"/>
+    <col min="6" max="6" width="32" customWidth="1"/>
+    <col min="7" max="7" width="19.625" customWidth="1"/>
+    <col min="8" max="8" width="18.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="15">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2533,31 +2512,49 @@
         <v>183</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>191</v>
+        <v>235</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>184</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I1" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="33">
-      <c r="A3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B3" s="2"/>
+    <row r="3" spans="1:8" s="2" customFormat="1" ht="33">
+      <c r="A3" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D3" s="2">
+        <v>100</v>
+      </c>
       <c r="E3" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>236</v>
       </c>
+      <c r="G3" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="B4" s="2"/>
+      <c r="F4" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B4">
       <formula1>cat</formula1>
     </dataValidation>
   </dataValidations>
@@ -2643,7 +2640,7 @@
         <v>203</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2832,7 +2829,7 @@
     </row>
     <row r="16" spans="2:2">
       <c r="B16" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="239">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1052,8 +1052,13 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>bb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>"wid":32,"hei":32,
-"key":"icons","frame":"312"</t>
+"key":"icons","frame":"312",
+"lit": true</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2488,9 +2493,9 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="12.625" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="30.625" customWidth="1"/>
-    <col min="6" max="6" width="32" customWidth="1"/>
+    <col min="4" max="4" width="7.875" customWidth="1"/>
+    <col min="5" max="5" width="26.75" customWidth="1"/>
+    <col min="6" max="6" width="23.125" customWidth="1"/>
     <col min="7" max="7" width="19.625" customWidth="1"/>
     <col min="8" max="8" width="18.625" customWidth="1"/>
   </cols>
@@ -2509,7 +2514,7 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>183</v>
+        <v>237</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>235</v>
@@ -2521,7 +2526,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="2" customFormat="1" ht="33">
+    <row r="3" spans="1:8" s="2" customFormat="1" ht="49.5">
       <c r="A3" s="2" t="s">
         <v>216</v>
       </c>
@@ -2535,7 +2540,7 @@
         <v>100</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>236</v>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="7290" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="7290" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="equips" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="244">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1059,6 +1059,28 @@
     <t>"wid":32,"hei":32,
 "key":"icons","frame":"312",
 "lit": true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"cps":5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"Plet",
+"des":""</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"lab":"毛皮",
+"des":"從動物身上剝下來、帶有毛髮的完整皮毛。"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:280</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2734,8 +2756,28 @@
     <row r="4" spans="1:11">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="3"/>
+    <row r="5" spans="1:11" ht="60">
+      <c r="A5" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D5" s="2">
+        <v>10</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="3"/>
@@ -2743,7 +2785,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B6 B8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8 B3:B6">
       <formula1>cat</formula1>
     </dataValidation>
   </dataValidations>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="243">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -837,10 +837,6 @@
   </si>
   <si>
     <t>assets_spritesheet_v2_free/028.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"cps":10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1498,7 +1494,7 @@
         <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>134</v>
@@ -1507,7 +1503,7 @@
         <v>135</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>65</v>
@@ -1956,7 +1952,7 @@
         <v>14</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D22" s="2">
         <v>10</v>
@@ -1976,7 +1972,7 @@
         <v>15</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D23" s="2">
         <v>10</v>
@@ -1990,13 +1986,13 @@
     </row>
     <row r="26" spans="1:12" ht="30">
       <c r="A26" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D26" s="2">
         <v>10</v>
@@ -2008,13 +2004,13 @@
         <v>136</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -2068,13 +2064,13 @@
         <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>65</v>
@@ -2091,7 +2087,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D3" s="2">
         <v>10</v>
@@ -2111,7 +2107,7 @@
         <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D4" s="2">
         <v>10</v>
@@ -2134,7 +2130,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D6" s="2">
         <v>10</v>
@@ -2157,7 +2153,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D7" s="2">
         <v>10</v>
@@ -2277,13 +2273,13 @@
         <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>65</v>
@@ -2300,7 +2296,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D3" s="2">
         <v>10</v>
@@ -2326,7 +2322,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D4" s="2">
         <v>15</v>
@@ -2352,7 +2348,7 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D5" s="2">
         <v>10</v>
@@ -2378,7 +2374,7 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D6" s="2">
         <v>15</v>
@@ -2404,7 +2400,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D8" s="2">
         <v>10</v>
@@ -2421,13 +2417,13 @@
     </row>
     <row r="10" spans="1:11" ht="30">
       <c r="A10" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D10" s="2">
         <v>10</v>
@@ -2436,24 +2432,24 @@
         <v>149</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="30">
       <c r="A11" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D11" s="2">
         <v>10</v>
@@ -2462,24 +2458,24 @@
         <v>149</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J11" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="30">
       <c r="A12" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D12" s="2">
         <v>5</v>
@@ -2488,13 +2484,13 @@
         <v>149</v>
       </c>
       <c r="I12" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -2536,10 +2532,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>65</v>
@@ -2550,28 +2546,28 @@
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="49.5">
       <c r="A3" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D3" s="2">
         <v>100</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2623,7 +2619,7 @@
         <v>183</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>184</v>
@@ -2643,31 +2639,31 @@
         <v>182</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="60">
       <c r="A4" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="60">
       <c r="A5" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="45">
       <c r="A6" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -2689,8 +2685,8 @@
     <col min="6" max="6" width="6.125" style="2" customWidth="1"/>
     <col min="7" max="7" width="6.375" style="2" customWidth="1"/>
     <col min="8" max="8" width="8.125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="10.75" style="2" customWidth="1"/>
-    <col min="10" max="10" width="21.375" style="2"/>
+    <col min="9" max="9" width="9.375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="33.25" style="2" customWidth="1"/>
     <col min="11" max="11" width="28" style="2" customWidth="1"/>
     <col min="12" max="16384" width="21.375" style="2"/>
   </cols>
@@ -2715,13 +2711,13 @@
         <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>65</v>
@@ -2744,7 +2740,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>189</v>
+        <v>38</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>187</v>
@@ -2758,25 +2754,25 @@
     </row>
     <row r="5" spans="1:11" ht="60">
       <c r="A5" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D5" s="2">
         <v>10</v>
       </c>
       <c r="I5" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2876,7 +2872,7 @@
     </row>
     <row r="16" spans="2:2">
       <c r="B16" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -2678,15 +2678,15 @@
   <sheetFormatPr defaultColWidth="21.375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.75" style="2" customWidth="1"/>
-    <col min="2" max="2" width="21.375" style="2"/>
-    <col min="3" max="3" width="33.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="31.25" style="2" customWidth="1"/>
     <col min="4" max="4" width="6" style="2" customWidth="1"/>
     <col min="5" max="5" width="7" style="2" customWidth="1"/>
     <col min="6" max="6" width="6.125" style="2" customWidth="1"/>
     <col min="7" max="7" width="6.375" style="2" customWidth="1"/>
     <col min="8" max="8" width="8.125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9.375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="33.25" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="44.375" style="2" customWidth="1"/>
     <col min="11" max="11" width="28" style="2" customWidth="1"/>
     <col min="12" max="16384" width="21.375" style="2"/>
   </cols>
@@ -2752,7 +2752,7 @@
     <row r="4" spans="1:11">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:11" ht="60">
+    <row r="5" spans="1:11" ht="44.25" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>238</v>
       </c>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="7290" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="7290" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="equips" sheetId="1" r:id="rId1"/>
@@ -979,10 +979,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>icons:237</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>icons:170</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1077,6 +1073,10 @@
   </si>
   <si>
     <t>icons:280</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icons:137</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2107,7 +2107,7 @@
         <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D4" s="2">
         <v>10</v>
@@ -2130,7 +2130,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D6" s="2">
         <v>10</v>
@@ -2153,7 +2153,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D7" s="2">
         <v>10</v>
@@ -2296,7 +2296,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D3" s="2">
         <v>10</v>
@@ -2322,7 +2322,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D4" s="2">
         <v>15</v>
@@ -2348,7 +2348,7 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D5" s="2">
         <v>10</v>
@@ -2374,7 +2374,7 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D6" s="2">
         <v>15</v>
@@ -2400,7 +2400,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D8" s="2">
         <v>10</v>
@@ -2423,7 +2423,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D10" s="2">
         <v>10</v>
@@ -2449,7 +2449,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D11" s="2">
         <v>10</v>
@@ -2475,7 +2475,7 @@
         <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D12" s="2">
         <v>5</v>
@@ -2532,10 +2532,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>65</v>
@@ -2549,19 +2549,19 @@
         <v>215</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D3" s="2">
         <v>100</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>214</v>
@@ -2663,7 +2663,7 @@
         <v>202</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -2754,25 +2754,25 @@
     </row>
     <row r="5" spans="1:11" ht="44.25" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D5" s="2">
         <v>10</v>
       </c>
       <c r="I5" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2872,7 +2872,7 @@
     </row>
     <row r="16" spans="2:2">
       <c r="B16" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="7290" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="7290"/>
   </bookViews>
   <sheets>
     <sheet name="equips" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="244">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1077,6 +1077,10 @@
   </si>
   <si>
     <t>icons:137</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"sprite":"weapons:6","y":22</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1998,7 +2002,7 @@
         <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>145</v>
+        <v>243</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>136</v>

--- a/xls/item.xlsx
+++ b/xls/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="7290"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="7290" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="equips" sheetId="1" r:id="rId1"/>
@@ -806,14 +806,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"anchorX":0,"anchorY":48,
-"bl":10,"br":10,"bt":96,
-"gl":10,"gr":10,"gt":96,
-"zl":10,"zr":10,"zt":96,
-"isBlock":true,"weight":-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>bb_view</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1081,6 +1073,14 @@
   </si>
   <si>
     <t>"sprite":"weapons:6","y":22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"ab":32,
+"bl":16,"bw":32,"bh":32,
+"gl":16,"gw":32,"gh":32,
+"zl":16,"zw":32,"zh":32,
+"weight":-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1498,7 +1498,7 @@
         <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>134</v>
@@ -1507,7 +1507,7 @@
         <v>135</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>65</v>
@@ -1956,7 +1956,7 @@
         <v>14</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D22" s="2">
         <v>10</v>
@@ -1976,7 +1976,7 @@
         <v>15</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D23" s="2">
         <v>10</v>
@@ -1990,31 +1990,31 @@
     </row>
     <row r="26" spans="1:12" ht="30">
       <c r="A26" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D26" s="2">
         <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>136</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -2068,13 +2068,13 @@
         <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>65</v>
@@ -2091,7 +2091,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D3" s="2">
         <v>10</v>
@@ -2111,7 +2111,7 @@
         <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D4" s="2">
         <v>10</v>
@@ -2134,7 +2134,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D6" s="2">
         <v>10</v>
@@ -2157,7 +2157,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D7" s="2">
         <v>10</v>
@@ -2277,13 +2277,13 @@
         <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>65</v>
@@ -2300,7 +2300,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D3" s="2">
         <v>10</v>
@@ -2326,7 +2326,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D4" s="2">
         <v>15</v>
@@ -2352,7 +2352,7 @@
         <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D5" s="2">
         <v>10</v>
@@ -2378,7 +2378,7 @@
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D6" s="2">
         <v>15</v>
@@ -2404,7 +2404,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D8" s="2">
         <v>10</v>
@@ -2421,13 +2421,13 @@
     </row>
     <row r="10" spans="1:11" ht="30">
       <c r="A10" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D10" s="2">
         <v>10</v>
@@ -2436,24 +2436,24 @@
         <v>149</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="30">
       <c r="A11" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D11" s="2">
         <v>10</v>
@@ -2462,24 +2462,24 @@
         <v>149</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J11" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="30">
       <c r="A12" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D12" s="2">
         <v>5</v>
@@ -2488,13 +2488,13 @@
         <v>149</v>
       </c>
       <c r="I12" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -2536,10 +2536,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>65</v>
@@ -2550,28 +2550,28 @@
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="49.5">
       <c r="A3" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D3" s="2">
         <v>100</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2620,13 +2620,13 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>184</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>65</v>
@@ -2640,34 +2640,34 @@
         <v>181</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>182</v>
+        <v>243</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="60">
       <c r="A4" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="60">
       <c r="A5" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="45">
       <c r="A6" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -2715,13 +2715,13 @@
         <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>134</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>65</v>
@@ -2732,13 +2732,13 @@
     </row>
     <row r="3" spans="1:11" ht="30">
       <c r="A3" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -2747,10 +2747,10 @@
         <v>38</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2758,25 +2758,25 @@
     </row>
     <row r="5" spans="1:11" ht="44.25" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D5" s="2">
         <v>10</v>
       </c>
       <c r="I5" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2876,7 +2876,7 @@
     </row>
     <row r="16" spans="2:2">
       <c r="B16" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
